--- a/Dataset description/IDS mapping.xlsx
+++ b/Dataset description/IDS mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6122549155ddafb1/Documents/GitHub/ResearchProject/Dataset description/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_F25DC773A252ABDACC10482FB99E48125BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E14CF7B4-5CC9-4E1A-806B-90FBC4C67827}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_F25DC773A252ABDACC10482FB99E48125BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE1BE3D0-1899-4734-9058-5A9A83C76BBB}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="93">
   <si>
     <t>admission_type_id</t>
   </si>
@@ -211,6 +211,99 @@
   </si>
   <si>
     <t>Description</t>
+  </si>
+  <si>
+    <t>patients needed immediate care</t>
+  </si>
+  <si>
+    <t>patient needed care quickly</t>
+  </si>
+  <si>
+    <t>planned hospital admission</t>
+  </si>
+  <si>
+    <t>admission for serious injury</t>
+  </si>
+  <si>
+    <t>Transferred to a skilled nursing facility</t>
+  </si>
+  <si>
+    <t>Transferred to an intermediate care facility</t>
+  </si>
+  <si>
+    <t>Left the hospital against medical advice</t>
+  </si>
+  <si>
+    <t>Referred by a doctor</t>
+  </si>
+  <si>
+    <t>Referred by a clinic</t>
+  </si>
+  <si>
+    <t>Transferred from another hospital</t>
+  </si>
+  <si>
+    <t>Transferred from a skilled nursing facility</t>
+  </si>
+  <si>
+    <t>Transferred from another healthcare facility</t>
+  </si>
+  <si>
+    <t>Came through the emergency room</t>
+  </si>
+  <si>
+    <t>Sent by a court or law enforcement</t>
+  </si>
+  <si>
+    <t>Information not available</t>
+  </si>
+  <si>
+    <t>Transferred from a critical access hospital</t>
+  </si>
+  <si>
+    <t>Normal birth</t>
+  </si>
+  <si>
+    <t>Premature birth</t>
+  </si>
+  <si>
+    <t>Sick newborn</t>
+  </si>
+  <si>
+    <t>Born outside the hospital</t>
+  </si>
+  <si>
+    <t>Missing – no information recorded</t>
+  </si>
+  <si>
+    <t>Transferred from another home healthcare provider</t>
+  </si>
+  <si>
+    <t>Readmitted to the same home healthcare provider</t>
+  </si>
+  <si>
+    <t>Not mapped – no description available</t>
+  </si>
+  <si>
+    <t>Unknown or invalid information</t>
+  </si>
+  <si>
+    <t>Transferred from another hospital department or facility</t>
+  </si>
+  <si>
+    <t>Born inside this hospital</t>
+  </si>
+  <si>
+    <t>Born outside this hospital</t>
+  </si>
+  <si>
+    <t>Transferred from hospice care</t>
+  </si>
+  <si>
+    <t>official approval from the primary care doctor that lets the patient see a medical specialist</t>
+  </si>
+  <si>
+    <t>Transferred from an outpatient surgery center to a full service hospital for high level care</t>
   </si>
 </sst>
 </file>
@@ -254,9 +347,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -537,542 +642,640 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B68"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="31" style="1" customWidth="1"/>
-    <col min="2" max="2" width="71.5546875" customWidth="1"/>
+    <col min="2" max="2" width="34" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>1</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>2</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>3</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" ht="29.4" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>4</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>5</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>6</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>7</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>8</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>9</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>10</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>11</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>12</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>13</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>14</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>15</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>16</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>17</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>18</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>19</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>20</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>21</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>22</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>23</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>24</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>25</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>26</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>30</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>27</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>28</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>29</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="C43" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" s="1">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="5">
         <v>1</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C44" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" s="1">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="5">
         <v>2</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C45" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" s="1">
+    <row r="46" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A46" s="5">
         <v>3</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C46" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" s="1">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="5">
         <v>4</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A48" s="1">
+    <row r="48" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="5">
         <v>5</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C48" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A49" s="1">
+    <row r="49" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="5">
         <v>6</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C49" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A50" s="1">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="5">
         <v>7</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C50" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A51" s="1">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="5">
         <v>8</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C51" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A52" s="1">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="5">
         <v>9</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C52" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A53" s="1">
+    <row r="53" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="5">
         <v>10</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C53" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A54" s="1">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="5">
         <v>11</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A55" s="1">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="5">
         <v>12</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C55" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A56" s="1">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="5">
         <v>13</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C56" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A57" s="1">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="5">
         <v>14</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C57" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A58" s="1">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="5">
         <v>15</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C58" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A59" s="1">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="5">
         <v>17</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C59" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A60" s="1">
+    <row r="60" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A60" s="5">
         <v>18</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C60" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A61" s="1">
+    <row r="61" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A61" s="5">
         <v>19</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C61" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A62" s="1">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="5">
         <v>20</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C62" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A63" s="1">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="5">
         <v>21</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C63" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A64" s="1">
+    <row r="64" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A64" s="5">
         <v>22</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C64" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A65" s="1">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="5">
         <v>23</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C65" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A66" s="1">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="5">
         <v>24</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C66" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A67" s="1">
+    <row r="67" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A67" s="5">
         <v>25</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C67" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A68" s="1">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="5">
         <v>26</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C68" t="s">
         <v>60</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>